--- a/public/templates/fuel-template.xlsx
+++ b/public/templates/fuel-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthika Suresh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hackathon\ESGroww\ESGroww\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BF861DA-3A55-4606-94F6-35A85EA60E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF1354F-8AD9-451D-98BD-D8A803A795BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4FF0677B-3B9D-4E7D-A727-B3763C791967}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{4FF0677B-3B9D-4E7D-A727-B3763C791967}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,22 +34,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>dgDieselLitres</t>
+  </si>
+  <si>
+    <t>⛽  Fuel / DG Consumption Upload Template</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>DG_Runtime_Hours</t>
+  </si>
+  <si>
+    <t>Diesel_Cost</t>
+  </si>
+  <si>
+    <t>PNG_CNG_Quantity</t>
+  </si>
+  <si>
+    <t>Month of data entry. Enter as number (1–12) or text (Jan–Dec / January–December).</t>
+  </si>
+  <si>
+    <t>4-digit calendar year of the data entry.</t>
+  </si>
+  <si>
+    <t>Total diesel / HSD consumed by diesel generator(s) during the month, in litres.</t>
+  </si>
+  <si>
+    <t>Total hours the diesel generator(s) were in operation during the month.</t>
+  </si>
+  <si>
+    <t>Total fuel expenditure for the month (diesel purchases). In INR. Optional.</t>
+  </si>
+  <si>
+    <t>Quantity of piped natural gas (PNG) or compressed natural gas (CNG) consumed, in kg. Enter 0 if not applicable.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -57,16 +87,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF1A5276"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A5276"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF117A65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -74,12 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -394,21 +484,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB478A80-3E27-4361-9A5E-FD53C132FFC5}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/templates/fuel-template.xlsx
+++ b/public/templates/fuel-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hackathon\ESGroww\ESGroww\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthika\Desktop\ESGroww\ESGroww\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF1354F-8AD9-451D-98BD-D8A803A795BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56AF156-EFC8-4DE0-B617-8B45FFF20930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{4FF0677B-3B9D-4E7D-A727-B3763C791967}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4FF0677B-3B9D-4E7D-A727-B3763C791967}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,15 +39,6 @@
     <t>dgDieselLitres</t>
   </si>
   <si>
-    <t>⛽  Fuel / DG Consumption Upload Template</t>
-  </si>
-  <si>
-    <t>month</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
     <t>DG_Runtime_Hours</t>
   </si>
   <si>
@@ -73,6 +64,15 @@
   </si>
   <si>
     <t>Quantity of piped natural gas (PNG) or compressed natural gas (CNG) consumed, in kg. Enter 0 if not applicable.</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>⛽  Fuel Consumption Upload Template</t>
   </si>
 </sst>
 </file>
@@ -161,14 +161,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -495,53 +495,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
